--- a/IT Questions (2).xlsx
+++ b/IT Questions (2).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4569" uniqueCount="2767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4569" uniqueCount="2766">
   <si>
     <t>Q#</t>
   </si>
@@ -157,16 +157,16 @@
     <t>What feature in word allows you to track changes made to a document</t>
   </si>
   <si>
-    <t>track change</t>
-  </si>
-  <si>
-    <t>comments</t>
-  </si>
-  <si>
-    <t>document inspector</t>
-  </si>
-  <si>
-    <t>compare</t>
+    <t>Track change</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Document inspector</t>
+  </si>
+  <si>
+    <t>Compare</t>
   </si>
   <si>
     <t>_________ Section break inserts the section break and then starts the new section on the next odd or even numbered page.</t>
@@ -1333,7 +1333,7 @@
     <t>data</t>
   </si>
   <si>
-    <t>Data Tables allow you to perform a one-variable or two-variable analysis of a formula</t>
+    <t xml:space="preserve"> _________ allow you to perform a one-variable or two-variable analysis of a formula</t>
   </si>
   <si>
     <t>By using Goal Seek, we can quickly determine _________ we are required to achieve</t>
@@ -3028,7 +3028,10 @@
     <t>Which website should you visit to initiate income tax registration?</t>
   </si>
   <si>
-    <t>[link removed]</t>
+    <t>https://www.incometax.gov</t>
+  </si>
+  <si>
+    <t>https://www.taxregistration.gov</t>
   </si>
   <si>
     <t>https://www.irs.gov</t>
@@ -3259,7 +3262,7 @@
     <t>To report the details of tax payments made to the government</t>
   </si>
   <si>
-    <t>In GSTR-1 B2C large applicable for</t>
+    <t>In GSTR-1 B2C largely applicable for</t>
   </si>
   <si>
     <t>Inter-state outward supplies to an unregistered person having an invoice value greater than 250000</t>
@@ -5284,9 +5287,6 @@
     <t>Append</t>
   </si>
   <si>
-    <t>Compare</t>
-  </si>
-  <si>
     <t>In CaseWare IDEA, which of the following options can be used to determine the change in the value of individual assets from the previous year?</t>
   </si>
   <si>
@@ -5524,7 +5524,7 @@
     <t>Zoho Evolve</t>
   </si>
   <si>
-    <t>Zoho Crm</t>
+    <t>Zoho CRM</t>
   </si>
   <si>
     <t>Zoho Invoice</t>
@@ -5551,7 +5551,7 @@
     <t>All Of The Above</t>
   </si>
   <si>
-    <t>In Zoho Book Where We Found General Ledger Option</t>
+    <t>In Zoho Book Where We Find General Ledger Option</t>
   </si>
   <si>
     <t>Balance Sheet</t>
@@ -5854,7 +5854,7 @@
     <t>Purchase Orders</t>
   </si>
   <si>
-    <t>In Zoho Book What Is The Purpose Of The "Brs" Feature</t>
+    <t>In Zoho Book What Is The Purpose Of The "BRS" Feature</t>
   </si>
   <si>
     <t>To Track Expenses</t>
@@ -6091,7 +6091,7 @@
     <t>It Is The Sum Of All Expenses For The Period</t>
   </si>
   <si>
-    <t>Which Module Allows You To Add Additional Details Or Attachments During Reconciliation</t>
+    <t>Which Module Allows You To Add Additional Details or Attachments During Reconciliation</t>
   </si>
   <si>
     <t>Documents</t>
@@ -6355,13 +6355,13 @@
     <t>Silicon Valley, USA</t>
   </si>
   <si>
-    <t>Tokyo Japan</t>
-  </si>
-  <si>
-    <t>Bangalore India</t>
-  </si>
-  <si>
-    <t>London UK</t>
+    <t>Tokyo, Japan</t>
+  </si>
+  <si>
+    <t>Bangalore, India</t>
+  </si>
+  <si>
+    <t>London, UK</t>
   </si>
   <si>
     <t>How Can You Track Expenses In Zoho Books</t>
@@ -7813,13 +7813,10 @@
     <t>Which Oracle Fusion Component Is Designed For Financial Management</t>
   </si>
   <si>
-    <t>Hcm</t>
-  </si>
-  <si>
-    <t>Crm</t>
-  </si>
-  <si>
-    <t>Scm</t>
+    <t>HCM</t>
+  </si>
+  <si>
+    <t>SCM</t>
   </si>
   <si>
     <t>Financials</t>
@@ -7840,7 +7837,7 @@
     <t>Third Party Technology</t>
   </si>
   <si>
-    <t>Oracle Fusion Crm Primarily Focuses On Which Area</t>
+    <t>Oracle Fusion CRM Primarily Focuses On Which Area</t>
   </si>
   <si>
     <t>Financial Management</t>
@@ -8002,7 +7999,7 @@
     <t>To Replace Oracle'S Hardware Systems</t>
   </si>
   <si>
-    <t>To Integrate And Modernize Oracle'S Existing Erp Offerings</t>
+    <t>To Integrate And Modernize Oracle'S Existing ERP Offerings</t>
   </si>
   <si>
     <t>To Introduce New Hardware Solutions</t>
@@ -8089,7 +8086,7 @@
     <t>Oracle Fusion Financials</t>
   </si>
   <si>
-    <t>Oracle Fusion Hcm</t>
+    <t>Oracle Fusion HCM</t>
   </si>
   <si>
     <t>Oracle Fusion Audit</t>
@@ -8134,7 +8131,7 @@
     <t>Oracle Fusion Payroll</t>
   </si>
   <si>
-    <t>Oracle Fusion Human Capital Management(Hcm)</t>
+    <t>Oracle Fusion Human Capital Management(HCM)</t>
   </si>
   <si>
     <t>What Does The O2C Process In Oracle Fusion Stand For</t>
@@ -8197,16 +8194,16 @@
     <t>Which Module In Oracle Fusion Is Used For Managing Financial Transactions</t>
   </si>
   <si>
-    <t>Fusion Hcm</t>
-  </si>
-  <si>
-    <t>Fusion Crm</t>
+    <t>Fusion HCM</t>
+  </si>
+  <si>
+    <t>Fusion CRM</t>
   </si>
   <si>
     <t>Fusion Financials</t>
   </si>
   <si>
-    <t>Fusion Scm</t>
+    <t>Fusion SCM</t>
   </si>
   <si>
     <t>What Is The Primary Purpose Of Oracle Fusion Project Portfolio Management</t>
@@ -8272,7 +8269,7 @@
     <t>Social Media Integration</t>
   </si>
   <si>
-    <t>Enterprise Resource Planning(Erp) And Cloud Based Application</t>
+    <t>Enterprise Resource Planning(ERP) And Cloud Based Application</t>
   </si>
   <si>
     <t>Mobile App Development</t>
@@ -8318,7 +8315,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -8347,6 +8344,11 @@
       <b/>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
       <name val="Roboto"/>
     </font>
   </fonts>
@@ -8432,7 +8434,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -8469,6 +8471,9 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf quotePrefix="1" borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf quotePrefix="1" borderId="1" fillId="4" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
@@ -14931,17 +14936,17 @@
       <c r="C243" s="7" t="s">
         <v>1004</v>
       </c>
-      <c r="D243" s="7" t="s">
+      <c r="D243" s="14" t="s">
         <v>1005</v>
       </c>
-      <c r="E243" s="7" t="s">
-        <v>1005</v>
+      <c r="E243" s="14" t="s">
+        <v>1006</v>
       </c>
       <c r="F243" s="7" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G243" s="7" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H243" s="8" t="s">
         <v>38</v>
@@ -14955,19 +14960,19 @@
         <v>993</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D244" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E244" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F244" s="7" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="G244" s="7" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H244" s="8" t="s">
         <v>38</v>
@@ -14981,19 +14986,19 @@
         <v>993</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D245" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="E245" s="7" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F245" s="7" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G245" s="7" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H245" s="8" t="s">
         <v>27</v>
@@ -15007,16 +15012,16 @@
         <v>993</v>
       </c>
       <c r="C246" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D246" s="7" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E246" s="7" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F246" s="7" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="G246" s="7" t="s">
         <v>152</v>
@@ -15033,19 +15038,19 @@
         <v>993</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D247" s="7" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F247" s="7" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="G247" s="7" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H247" s="8" t="s">
         <v>21</v>
@@ -15059,19 +15064,19 @@
         <v>993</v>
       </c>
       <c r="C248" s="7" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D248" s="7" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="E248" s="7" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F248" s="7" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="G248" s="7" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H248" s="8" t="s">
         <v>15</v>
@@ -15085,19 +15090,19 @@
         <v>993</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D249" s="7" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E249" s="7" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F249" s="7" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="G249" s="7" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H249" s="8" t="s">
         <v>27</v>
@@ -15111,19 +15116,19 @@
         <v>993</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D250" s="7" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E250" s="7" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F250" s="7" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G250" s="7" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H250" s="8" t="s">
         <v>27</v>
@@ -15137,19 +15142,19 @@
         <v>993</v>
       </c>
       <c r="C251" s="7" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D251" s="7" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="E251" s="7" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="F251" s="7" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="G251" s="7" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H251" s="8" t="s">
         <v>27</v>
@@ -15163,19 +15168,19 @@
         <v>993</v>
       </c>
       <c r="C252" s="7" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D252" s="7" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="E252" s="7" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F252" s="7" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="G252" s="7" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H252" s="8" t="s">
         <v>27</v>
@@ -15189,19 +15194,19 @@
         <v>993</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D253" s="7" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="E253" s="7" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F253" s="7" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="G253" s="7" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H253" s="8" t="s">
         <v>38</v>
@@ -15215,19 +15220,19 @@
         <v>993</v>
       </c>
       <c r="C254" s="7" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D254" s="7" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="E254" s="7" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F254" s="7" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="G254" s="7" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H254" s="8" t="s">
         <v>15</v>
@@ -15241,19 +15246,19 @@
         <v>993</v>
       </c>
       <c r="C255" s="7" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D255" s="7" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E255" s="7" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F255" s="7" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="G255" s="7" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H255" s="8" t="s">
         <v>38</v>
@@ -15267,19 +15272,19 @@
         <v>993</v>
       </c>
       <c r="C256" s="7" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D256" s="7" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="E256" s="7" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F256" s="7" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="G256" s="7" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H256" s="8" t="s">
         <v>15</v>
@@ -15293,19 +15298,19 @@
         <v>993</v>
       </c>
       <c r="C257" s="7" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D257" s="7" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="E257" s="7" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F257" s="7" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="G257" s="7" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H257" s="8" t="s">
         <v>27</v>
@@ -15319,19 +15324,19 @@
         <v>993</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D258" s="7" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="E258" s="7" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F258" s="7" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="G258" s="7" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H258" s="8" t="s">
         <v>15</v>
@@ -15345,19 +15350,19 @@
         <v>993</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D259" s="7" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="E259" s="7" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F259" s="7" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G259" s="7" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H259" s="8" t="s">
         <v>38</v>
@@ -15371,19 +15376,19 @@
         <v>993</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D260" s="7" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E260" s="7" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F260" s="7" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="G260" s="7" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H260" s="8" t="s">
         <v>15</v>
@@ -15397,19 +15402,19 @@
         <v>993</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D261" s="7" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E261" s="7" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F261" s="7" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="G261" s="7" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H261" s="8" t="s">
         <v>27</v>
@@ -15423,16 +15428,16 @@
         <v>993</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="D262" s="7" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="E262" s="7" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F262" s="7" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="G262" s="7" t="s">
         <v>152</v>
@@ -15449,19 +15454,19 @@
         <v>993</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D263" s="7" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E263" s="7" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F263" s="7" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="G263" s="7" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H263" s="8" t="s">
         <v>15</v>
@@ -15475,7 +15480,7 @@
         <v>993</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D264" s="7">
         <v>16.0</v>
@@ -15501,19 +15506,19 @@
         <v>993</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D265" s="7" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E265" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F265" s="7" t="s">
         <v>1104</v>
       </c>
-      <c r="F265" s="7" t="s">
-        <v>1103</v>
-      </c>
       <c r="G265" s="7" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H265" s="8" t="s">
         <v>15</v>
@@ -15521,7 +15526,7 @@
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -15536,22 +15541,22 @@
         <v>261.0</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D267" s="7" t="s">
         <v>411</v>
       </c>
       <c r="E267" s="7" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F267" s="7" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="G267" s="7" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H267" s="8" t="s">
         <v>27</v>
@@ -15562,22 +15567,22 @@
         <v>262.0</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D268" s="7" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E268" s="7" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F268" s="7" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="G268" s="7" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H268" s="8" t="s">
         <v>38</v>
@@ -15588,10 +15593,10 @@
         <v>263.0</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D269" s="7" t="s">
         <v>743</v>
@@ -15600,7 +15605,7 @@
         <v>91</v>
       </c>
       <c r="F269" s="7" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="G269" s="7" t="s">
         <v>92</v>
@@ -15614,22 +15619,22 @@
         <v>264.0</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D270" s="7" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="E270" s="7" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F270" s="7" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="G270" s="7" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H270" s="8" t="s">
         <v>27</v>
@@ -15640,22 +15645,22 @@
         <v>265.0</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D271" s="7" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E271" s="7" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F271" s="7" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G271" s="7" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H271" s="8" t="s">
         <v>15</v>
@@ -15666,22 +15671,22 @@
         <v>266.0</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D272" s="7" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="E272" s="7" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="F272" s="7" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="G272" s="7" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H272" s="8" t="s">
         <v>38</v>
@@ -15692,22 +15697,22 @@
         <v>267.0</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="D273" s="7" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="E273" s="7" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="F273" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="G273" s="7" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H273" s="8" t="s">
         <v>27</v>
@@ -15718,22 +15723,22 @@
         <v>268.0</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D274" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="E274" s="7" t="s">
         <v>848</v>
       </c>
       <c r="F274" s="7" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="G274" s="7" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H274" s="8" t="s">
         <v>15</v>
@@ -15744,22 +15749,22 @@
         <v>269.0</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D275" s="7" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="E275" s="7" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="F275" s="7" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="G275" s="7" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H275" s="8" t="s">
         <v>38</v>
@@ -15770,22 +15775,22 @@
         <v>270.0</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D276" s="7" t="s">
         <v>135</v>
       </c>
       <c r="E276" s="7" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="F276" s="7" t="s">
         <v>851</v>
       </c>
       <c r="G276" s="7" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H276" s="8" t="s">
         <v>21</v>
@@ -15796,22 +15801,22 @@
         <v>271.0</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D277" s="7" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="E277" s="7" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="F277" s="7" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="G277" s="7" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H277" s="8" t="s">
         <v>27</v>
@@ -15822,10 +15827,10 @@
         <v>272.0</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D278" s="7">
         <v>50.0</v>
@@ -15848,22 +15853,22 @@
         <v>273.0</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D279" s="7" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="E279" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F279" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G279" s="7" t="s">
         <v>1125</v>
-      </c>
-      <c r="F279" s="7" t="s">
-        <v>1160</v>
-      </c>
-      <c r="G279" s="7" t="s">
-        <v>1124</v>
       </c>
       <c r="H279" s="8" t="s">
         <v>21</v>
@@ -15874,22 +15879,22 @@
         <v>274.0</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D280" s="7" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="E280" s="7" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="F280" s="7" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="G280" s="7" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H280" s="8" t="s">
         <v>27</v>
@@ -15900,22 +15905,22 @@
         <v>275.0</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D281" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E281" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F281" s="7" t="s">
         <v>1140</v>
       </c>
-      <c r="E281" s="7" t="s">
-        <v>1137</v>
-      </c>
-      <c r="F281" s="7" t="s">
+      <c r="G281" s="7" t="s">
         <v>1139</v>
-      </c>
-      <c r="G281" s="7" t="s">
-        <v>1138</v>
       </c>
       <c r="H281" s="8" t="s">
         <v>27</v>
@@ -15926,22 +15931,22 @@
         <v>276.0</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D282" s="7" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="E282" s="7" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="F282" s="7" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="G282" s="7" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H282" s="8" t="s">
         <v>27</v>
@@ -15952,22 +15957,22 @@
         <v>277.0</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D283" s="7" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E283" s="7" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="F283" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G283" s="7" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H283" s="8" t="s">
         <v>15</v>
@@ -15978,22 +15983,22 @@
         <v>278.0</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D284" s="7" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="E284" s="7" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="F284" s="7" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="G284" s="7" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H284" s="8" t="s">
         <v>15</v>
@@ -16004,22 +16009,22 @@
         <v>279.0</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D285" s="7" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="E285" s="7" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F285" s="7" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="G285" s="7" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H285" s="8" t="s">
         <v>38</v>
@@ -16030,22 +16035,22 @@
         <v>280.0</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C286" s="7" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="D286" s="7" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="E286" s="7" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="F286" s="7" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="G286" s="7" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H286" s="8" t="s">
         <v>15</v>
@@ -16056,10 +16061,10 @@
         <v>281.0</v>
       </c>
       <c r="B287" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C287" s="7" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D287" s="7">
         <v>100.0</v>
@@ -16082,22 +16087,22 @@
         <v>282.0</v>
       </c>
       <c r="B288" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C288" s="7" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D288" s="7" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="E288" s="7" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="F288" s="7" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="G288" s="7" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H288" s="8" t="s">
         <v>21</v>
@@ -16108,22 +16113,22 @@
         <v>283.0</v>
       </c>
       <c r="B289" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C289" s="7" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D289" s="7" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E289" s="7" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F289" s="7" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="G289" s="7" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H289" s="8" t="s">
         <v>38</v>
@@ -16134,22 +16139,22 @@
         <v>284.0</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C290" s="7" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="D290" s="7" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="E290" s="7" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F290" s="7" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="G290" s="7" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H290" s="8" t="s">
         <v>27</v>
@@ -16160,22 +16165,22 @@
         <v>285.0</v>
       </c>
       <c r="B291" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C291" s="7" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="D291" s="7" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="E291" s="7" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="F291" s="7" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="G291" s="7" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H291" s="8" t="s">
         <v>27</v>
@@ -16186,22 +16191,22 @@
         <v>286.0</v>
       </c>
       <c r="B292" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C292" s="7" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D292" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="E292" s="7" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="F292" s="7" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="G292" s="7" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H292" s="8" t="s">
         <v>27</v>
@@ -16212,19 +16217,19 @@
         <v>287.0</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C293" s="7" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="D293" s="7" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="E293" s="7" t="s">
         <v>556</v>
       </c>
       <c r="F293" s="7" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="G293" s="7" t="s">
         <v>145</v>
@@ -16238,22 +16243,22 @@
         <v>288.0</v>
       </c>
       <c r="B294" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D294" s="7" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="E294" s="7" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="F294" s="7" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="G294" s="7" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H294" s="8" t="s">
         <v>27</v>
@@ -16264,22 +16269,22 @@
         <v>289.0</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C295" s="7" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="D295" s="7" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="E295" s="7" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="F295" s="7" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="G295" s="7" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H295" s="8" t="s">
         <v>27</v>
@@ -16290,22 +16295,22 @@
         <v>290.0</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C296" s="7" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="D296" s="7" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="E296" s="7" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F296" s="7" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="G296" s="7" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H296" s="8" t="s">
         <v>38</v>
@@ -16316,22 +16321,22 @@
         <v>291.0</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D297" s="7" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="E297" s="7" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="F297" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="G297" s="7" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H297" s="8" t="s">
         <v>27</v>
@@ -16342,22 +16347,22 @@
         <v>292.0</v>
       </c>
       <c r="B298" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="D298" s="7" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="F298" s="7" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="G298" s="7" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H298" s="8" t="s">
         <v>27</v>
@@ -16368,22 +16373,22 @@
         <v>293.0</v>
       </c>
       <c r="B299" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D299" s="7" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="E299" s="7" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="F299" s="7" t="s">
         <v>256</v>
       </c>
       <c r="G299" s="7" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H299" s="8" t="s">
         <v>27</v>
@@ -16394,22 +16399,22 @@
         <v>294.0</v>
       </c>
       <c r="B300" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="D300" s="7" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="E300" s="7" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="F300" s="7" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="G300" s="7" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H300" s="8" t="s">
         <v>27</v>
@@ -16420,22 +16425,22 @@
         <v>295.0</v>
       </c>
       <c r="B301" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C301" s="7" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D301" s="7" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="E301" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="F301" s="7" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="G301" s="7" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H301" s="8" t="s">
         <v>27</v>
@@ -16446,22 +16451,22 @@
         <v>296.0</v>
       </c>
       <c r="B302" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C302" s="7" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="D302" s="7" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="E302" s="7" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F302" s="7" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="G302" s="7" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H302" s="8" t="s">
         <v>15</v>
@@ -16472,22 +16477,22 @@
         <v>297.0</v>
       </c>
       <c r="B303" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C303" s="7" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D303" s="7" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="E303" s="7" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="F303" s="7" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="G303" s="7" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H303" s="8" t="s">
         <v>38</v>
@@ -16498,22 +16503,22 @@
         <v>298.0</v>
       </c>
       <c r="B304" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C304" s="7" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D304" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E304" s="7" t="s">
         <v>1211</v>
       </c>
-      <c r="E304" s="7" t="s">
+      <c r="F304" s="7" t="s">
         <v>1210</v>
       </c>
-      <c r="F304" s="7" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G304" s="14" t="s">
-        <v>1266</v>
+      <c r="G304" s="15" t="s">
+        <v>1267</v>
       </c>
       <c r="H304" s="8" t="s">
         <v>15</v>
@@ -16524,22 +16529,22 @@
         <v>299.0</v>
       </c>
       <c r="B305" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C305" s="7" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D305" s="7" t="s">
         <v>284</v>
       </c>
       <c r="E305" s="7" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="F305" s="7" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="G305" s="7" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H305" s="8" t="s">
         <v>38</v>
@@ -16550,22 +16555,22 @@
         <v>300.0</v>
       </c>
       <c r="B306" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D306" s="7" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="E306" s="7" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="F306" s="7" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="G306" s="7" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H306" s="8" t="s">
         <v>15</v>
@@ -16576,22 +16581,22 @@
         <v>301.0</v>
       </c>
       <c r="B307" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C307" s="7" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="D307" s="7" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="E307" s="7" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F307" s="7" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G307" s="7" t="s">
         <v>1263</v>
-      </c>
-      <c r="F307" s="7" t="s">
-        <v>1278</v>
-      </c>
-      <c r="G307" s="7" t="s">
-        <v>1262</v>
       </c>
       <c r="H307" s="8" t="s">
         <v>27</v>
@@ -16602,19 +16607,19 @@
         <v>302.0</v>
       </c>
       <c r="B308" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C308" s="7" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="D308" s="7" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="E308" s="7" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="F308" s="7" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="G308" s="7" t="s">
         <v>145</v>
@@ -16628,22 +16633,22 @@
         <v>303.0</v>
       </c>
       <c r="B309" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C309" s="7" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="D309" s="7" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="E309" s="7" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="F309" s="7" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G309" s="7" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H309" s="8" t="s">
         <v>27</v>
@@ -16654,22 +16659,22 @@
         <v>304.0</v>
       </c>
       <c r="B310" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C310" s="7" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="D310" s="7" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="E310" s="7" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="F310" s="7" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="G310" s="7" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H310" s="8" t="s">
         <v>15</v>
@@ -16680,22 +16685,22 @@
         <v>305.0</v>
       </c>
       <c r="B311" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C311" s="7" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="D311" s="7" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="E311" s="7" t="s">
         <v>741</v>
       </c>
       <c r="F311" s="7" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="G311" s="7" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H311" s="8" t="s">
         <v>15</v>
@@ -16706,22 +16711,22 @@
         <v>306.0</v>
       </c>
       <c r="B312" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C312" s="7" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D312" s="7" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="E312" s="7" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F312" s="7" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="G312" s="7" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H312" s="8" t="s">
         <v>27</v>
@@ -16732,22 +16737,22 @@
         <v>307.0</v>
       </c>
       <c r="B313" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C313" s="7" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="D313" s="7" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="E313" s="7" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="F313" s="7" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="G313" s="7" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H313" s="8" t="s">
         <v>21</v>
@@ -16758,22 +16763,22 @@
         <v>308.0</v>
       </c>
       <c r="B314" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C314" s="7" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D314" s="7" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="E314" s="7" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="F314" s="7" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G314" s="7" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H314" s="8" t="s">
         <v>15</v>
@@ -16784,22 +16789,22 @@
         <v>309.0</v>
       </c>
       <c r="B315" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C315" s="7" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D315" s="7" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="E315" s="7" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="F315" s="7" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="G315" s="7" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H315" s="8" t="s">
         <v>38</v>
@@ -16810,22 +16815,22 @@
         <v>310.0</v>
       </c>
       <c r="B316" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C316" s="7" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="D316" s="7" t="s">
         <v>556</v>
       </c>
       <c r="E316" s="7" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="F316" s="7" t="s">
         <v>541</v>
       </c>
       <c r="G316" s="7" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H316" s="8" t="s">
         <v>15</v>
@@ -16836,19 +16841,19 @@
         <v>311.0</v>
       </c>
       <c r="B317" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C317" s="7" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="D317" s="7" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="E317" s="7" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="F317" s="7" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="G317" s="7" t="s">
         <v>152</v>
@@ -16862,22 +16867,22 @@
         <v>312.0</v>
       </c>
       <c r="B318" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C318" s="7" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D318" s="7" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="E318" s="7" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="F318" s="7" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="G318" s="7" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H318" s="8" t="s">
         <v>38</v>
@@ -16888,22 +16893,22 @@
         <v>313.0</v>
       </c>
       <c r="B319" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C319" s="7" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D319" s="7" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E319" s="7" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="F319" s="7" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G319" s="7" t="s">
         <v>1138</v>
-      </c>
-      <c r="G319" s="7" t="s">
-        <v>1137</v>
       </c>
       <c r="H319" s="8" t="s">
         <v>27</v>
@@ -16914,22 +16919,22 @@
         <v>314.0</v>
       </c>
       <c r="B320" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C320" s="7" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="D320" s="7" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="E320" s="7" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="F320" s="7" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G320" s="7" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H320" s="8" t="s">
         <v>38</v>
@@ -16940,19 +16945,19 @@
         <v>315.0</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C321" s="7" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="D321" s="7" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="E321" s="7" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="F321" s="7" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="G321" s="7" t="s">
         <v>152</v>
@@ -16966,22 +16971,22 @@
         <v>316.0</v>
       </c>
       <c r="B322" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C322" s="7" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="D322" s="7" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E322" s="7" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="F322" s="7" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G322" s="7" t="s">
         <v>1138</v>
-      </c>
-      <c r="G322" s="7" t="s">
-        <v>1137</v>
       </c>
       <c r="H322" s="8" t="s">
         <v>15</v>
@@ -16992,19 +16997,19 @@
         <v>317.0</v>
       </c>
       <c r="B323" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C323" s="7" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="D323" s="7" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="E323" s="7" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="F323" s="7" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="G323" s="7" t="s">
         <v>152</v>
@@ -17018,22 +17023,22 @@
         <v>318.0</v>
       </c>
       <c r="B324" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C324" s="7" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="D324" s="7" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="E324" s="7" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="F324" s="7" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="G324" s="7" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H324" s="8" t="s">
         <v>15</v>
@@ -17044,19 +17049,19 @@
         <v>319.0</v>
       </c>
       <c r="B325" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C325" s="7" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="D325" s="7" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="E325" s="7" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="F325" s="7" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="G325" s="7" t="s">
         <v>145</v>
@@ -17070,22 +17075,22 @@
         <v>320.0</v>
       </c>
       <c r="B326" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C326" s="7" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="D326" s="7" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="E326" s="7" t="s">
         <v>500</v>
       </c>
       <c r="F326" s="7" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="G326" s="7" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H326" s="8" t="s">
         <v>38</v>
@@ -17096,22 +17101,22 @@
         <v>321.0</v>
       </c>
       <c r="B327" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C327" s="7" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D327" s="7" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="F327" s="7" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="G327" s="7" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H327" s="8" t="s">
         <v>15</v>
@@ -17122,22 +17127,22 @@
         <v>322.0</v>
       </c>
       <c r="B328" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C328" s="7" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="D328" s="7" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="E328" s="7" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="F328" s="7" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="G328" s="7" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H328" s="8" t="s">
         <v>15</v>
@@ -17148,22 +17153,22 @@
         <v>323.0</v>
       </c>
       <c r="B329" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C329" s="7" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="D329" s="7" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="E329" s="7" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="F329" s="7" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G329" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H329" s="8" t="s">
         <v>27</v>
@@ -17174,22 +17179,22 @@
         <v>324.0</v>
       </c>
       <c r="B330" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C330" s="7" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="D330" s="7" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="E330" s="7" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="F330" s="7" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="G330" s="7" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H330" s="8" t="s">
         <v>27</v>
@@ -17200,19 +17205,19 @@
         <v>325.0</v>
       </c>
       <c r="B331" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C331" s="7" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="D331" s="7" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="E331" s="7" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="F331" s="7" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="G331" s="7" t="s">
         <v>152</v>
@@ -17226,22 +17231,22 @@
         <v>326.0</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C332" s="7" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="D332" s="7" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="E332" s="7" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="F332" s="7" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="G332" s="7" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H332" s="8" t="s">
         <v>38</v>
@@ -17252,22 +17257,22 @@
         <v>327.0</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C333" s="7" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="D333" s="7" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="E333" s="7" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="F333" s="7" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="G333" s="7" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H333" s="8" t="s">
         <v>38</v>
@@ -17278,22 +17283,22 @@
         <v>328.0</v>
       </c>
       <c r="B334" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C334" s="7" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="D334" s="7" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="E334" s="7" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="F334" s="7" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="G334" s="7" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H334" s="8" t="s">
         <v>21</v>
@@ -17304,19 +17309,19 @@
         <v>329.0</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C335" s="7" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="D335" s="7" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="E335" s="7" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="F335" s="7" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="G335" s="7" t="s">
         <v>145</v>
@@ -17330,19 +17335,19 @@
         <v>330.0</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C336" s="7" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="D336" s="7" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="E336" s="7" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="F336" s="7" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="G336" s="7" t="s">
         <v>145</v>
@@ -17356,19 +17361,19 @@
         <v>331.0</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C337" s="7" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="D337" s="7" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="E337" s="7" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="F337" s="7" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="G337" s="7" t="s">
         <v>145</v>
@@ -17382,22 +17387,22 @@
         <v>332.0</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C338" s="7" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="D338" s="7" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="E338" s="7" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="F338" s="7" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="G338" s="7" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H338" s="8" t="s">
         <v>27</v>
@@ -17408,22 +17413,22 @@
         <v>333.0</v>
       </c>
       <c r="B339" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C339" s="7" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="D339" s="7" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="E339" s="7" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F339" s="7" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="G339" s="7" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H339" s="8" t="s">
         <v>27</v>
@@ -17434,22 +17439,22 @@
         <v>334.0</v>
       </c>
       <c r="B340" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C340" s="7" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="D340" s="7" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="E340" s="7" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="F340" s="7" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="G340" s="7" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H340" s="8" t="s">
         <v>38</v>
@@ -17460,22 +17465,22 @@
         <v>335.0</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C341" s="7" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="D341" s="7" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="E341" s="7" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="F341" s="7" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="G341" s="7" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H341" s="8" t="s">
         <v>27</v>
@@ -17486,22 +17491,22 @@
         <v>336.0</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C342" s="7" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="D342" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="E342" s="7" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="F342" s="7" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="G342" s="7" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H342" s="8" t="s">
         <v>38</v>
@@ -17512,22 +17517,22 @@
         <v>337.0</v>
       </c>
       <c r="B343" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C343" s="7" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="D343" s="7" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="E343" s="7" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="F343" s="7" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="G343" s="7" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H343" s="8" t="s">
         <v>15</v>
@@ -17538,22 +17543,22 @@
         <v>338.0</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C344" s="7" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="D344" s="7" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="E344" s="7" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="F344" s="7" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="G344" s="7" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H344" s="8" t="s">
         <v>38</v>
@@ -17564,22 +17569,22 @@
         <v>339.0</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C345" s="7" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D345" s="7" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="E345" s="7" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="F345" s="7" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="G345" s="7" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H345" s="8" t="s">
         <v>38</v>
@@ -17590,22 +17595,22 @@
         <v>340.0</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C346" s="7" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="D346" s="7" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="E346" s="7" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="F346" s="7" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="G346" s="7" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H346" s="8" t="s">
         <v>27</v>
@@ -17616,22 +17621,22 @@
         <v>341.0</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C347" s="7" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="D347" s="7" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="E347" s="7" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="F347" s="7" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G347" s="7" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H347" s="8" t="s">
         <v>15</v>
@@ -17642,22 +17647,22 @@
         <v>342.0</v>
       </c>
       <c r="B348" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C348" s="7" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D348" s="7" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="E348" s="7" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="F348" s="7" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="G348" s="7" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H348" s="8" t="s">
         <v>38</v>
@@ -17668,22 +17673,22 @@
         <v>343.0</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C349" s="7" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="D349" s="7" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="E349" s="7" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="F349" s="7" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="G349" s="7" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H349" s="8" t="s">
         <v>27</v>
@@ -17694,22 +17699,22 @@
         <v>344.0</v>
       </c>
       <c r="B350" s="9" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C350" s="10" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="D350" s="10" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="E350" s="10" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="F350" s="10" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="G350" s="10" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H350" s="11" t="s">
         <v>38</v>
@@ -17720,22 +17725,22 @@
         <v>345.0</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C351" s="7" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="D351" s="7" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="E351" s="7" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F351" s="7" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="G351" s="7" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H351" s="8" t="s">
         <v>27</v>
@@ -17746,22 +17751,22 @@
         <v>346.0</v>
       </c>
       <c r="B352" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C352" s="7" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="D352" s="7" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="E352" s="7" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="F352" s="7" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="G352" s="7" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H352" s="8" t="s">
         <v>38</v>
@@ -17772,22 +17777,22 @@
         <v>347.0</v>
       </c>
       <c r="B353" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C353" s="7" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="D353" s="7" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="E353" s="7" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="F353" s="7" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="G353" s="7" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H353" s="8" t="s">
         <v>27</v>
@@ -17798,19 +17803,19 @@
         <v>348.0</v>
       </c>
       <c r="B354" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C354" s="7" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="D354" s="7" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="E354" s="7" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="F354" s="7" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="G354" s="7" t="s">
         <v>145</v>
@@ -17824,19 +17829,19 @@
         <v>349.0</v>
       </c>
       <c r="B355" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C355" s="7" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="D355" s="7" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E355" s="7" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="F355" s="7" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="G355" s="7" t="s">
         <v>145</v>
@@ -17850,22 +17855,22 @@
         <v>350.0</v>
       </c>
       <c r="B356" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C356" s="7" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="D356" s="7" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="E356" s="7" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="F356" s="7" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="G356" s="7" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H356" s="8" t="s">
         <v>27</v>
@@ -17876,22 +17881,22 @@
         <v>351.0</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C357" s="7" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="D357" s="7" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="E357" s="7" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="F357" s="7" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="G357" s="7" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H357" s="8" t="s">
         <v>15</v>
@@ -17902,22 +17907,22 @@
         <v>352.0</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C358" s="7" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="D358" s="7" t="s">
         <v>770</v>
       </c>
       <c r="E358" s="7" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="F358" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="G358" s="7" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H358" s="8" t="s">
         <v>27</v>
@@ -17928,22 +17933,22 @@
         <v>353.0</v>
       </c>
       <c r="B359" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C359" s="7" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="D359" s="7" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="E359" s="7" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="F359" s="7" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="G359" s="7" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H359" s="8" t="s">
         <v>15</v>
@@ -17954,22 +17959,22 @@
         <v>354.0</v>
       </c>
       <c r="B360" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C360" s="7" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="D360" s="7" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="E360" s="7" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="F360" s="7" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="G360" s="7" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H360" s="8" t="s">
         <v>38</v>
@@ -17980,22 +17985,22 @@
         <v>355.0</v>
       </c>
       <c r="B361" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C361" s="7" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="D361" s="7" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="E361" s="7" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="F361" s="7" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="G361" s="7" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="H361" s="8" t="s">
         <v>21</v>
@@ -18006,22 +18011,22 @@
         <v>356.0</v>
       </c>
       <c r="B362" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C362" s="7" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="D362" s="7" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="E362" s="7" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="F362" s="7" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="G362" s="7" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="H362" s="8" t="s">
         <v>27</v>
@@ -18032,22 +18037,22 @@
         <v>357.0</v>
       </c>
       <c r="B363" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C363" s="7" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="D363" s="7" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="E363" s="7" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="F363" s="7" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="G363" s="7" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="H363" s="8" t="s">
         <v>38</v>
@@ -18058,22 +18063,22 @@
         <v>358.0</v>
       </c>
       <c r="B364" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C364" s="7" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="D364" s="7" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="E364" s="7" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="F364" s="7" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="G364" s="7" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="H364" s="8" t="s">
         <v>38</v>
@@ -18084,22 +18089,22 @@
         <v>359.0</v>
       </c>
       <c r="B365" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C365" s="7" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="D365" s="7" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="E365" s="7" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="F365" s="7" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="G365" s="7" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="H365" s="8" t="s">
         <v>27</v>
@@ -18110,22 +18115,22 @@
         <v>360.0</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C366" s="7" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="D366" s="7" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="E366" s="7" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="F366" s="7" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="G366" s="7" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="H366" s="8" t="s">
         <v>15</v>
@@ -18133,7 +18138,7 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -18148,22 +18153,22 @@
         <v>361.0</v>
       </c>
       <c r="B368" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C368" s="7" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="D368" s="7" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="E368" s="7" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="F368" s="7" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="G368" s="7" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H368" s="8" t="s">
         <v>27</v>
@@ -18174,22 +18179,22 @@
         <v>362.0</v>
       </c>
       <c r="B369" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C369" s="7" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="D369" s="7" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="E369" s="7" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="F369" s="7" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="G369" s="7" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="H369" s="8" t="s">
         <v>27</v>
@@ -18200,22 +18205,22 @@
         <v>363.0</v>
       </c>
       <c r="B370" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C370" s="7" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="D370" s="7" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="E370" s="7" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="F370" s="7" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="G370" s="7" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="H370" s="8" t="s">
         <v>15</v>
@@ -18226,22 +18231,22 @@
         <v>364.0</v>
       </c>
       <c r="B371" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C371" s="7" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="D371" s="7" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="E371" s="7" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="F371" s="7" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="G371" s="7" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="H371" s="8" t="s">
         <v>27</v>
@@ -18252,22 +18257,22 @@
         <v>365.0</v>
       </c>
       <c r="B372" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C372" s="7" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="D372" s="7" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="E372" s="7" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="F372" s="7" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="G372" s="7" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H372" s="8" t="s">
         <v>38</v>
@@ -18278,22 +18283,22 @@
         <v>366.0</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C373" s="7" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="D373" s="7" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="E373" s="7" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="F373" s="7" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="G373" s="7" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="H373" s="8" t="s">
         <v>15</v>
@@ -18304,22 +18309,22 @@
         <v>367.0</v>
       </c>
       <c r="B374" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C374" s="7" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="D374" s="7" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="E374" s="7" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="F374" s="7" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="G374" s="7" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="H374" s="8" t="s">
         <v>15</v>
@@ -18330,22 +18335,22 @@
         <v>368.0</v>
       </c>
       <c r="B375" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C375" s="7" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="D375" s="7" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="E375" s="7" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="F375" s="7" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G375" s="7" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="H375" s="8" t="s">
         <v>15</v>
@@ -18356,22 +18361,22 @@
         <v>369.0</v>
       </c>
       <c r="B376" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C376" s="7" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="D376" s="7" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="E376" s="7" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="F376" s="7" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="G376" s="7" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H376" s="8" t="s">
         <v>38</v>
@@ -18382,22 +18387,22 @@
         <v>370.0</v>
       </c>
       <c r="B377" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C377" s="7" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="D377" s="7" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="E377" s="7" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F377" s="7" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="G377" s="7" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H377" s="8" t="s">
         <v>38</v>
@@ -18408,22 +18413,22 @@
         <v>371.0</v>
       </c>
       <c r="B378" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C378" s="7" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="D378" s="7" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="E378" s="7" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="F378" s="7" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G378" s="7" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="H378" s="8" t="s">
         <v>27</v>
@@ -18434,22 +18439,22 @@
         <v>372.0</v>
       </c>
       <c r="B379" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C379" s="7" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="D379" s="7" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="E379" s="7" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="F379" s="7" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="G379" s="7" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H379" s="8" t="s">
         <v>21</v>
@@ -18460,22 +18465,22 @@
         <v>373.0</v>
       </c>
       <c r="B380" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C380" s="7" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="D380" s="7" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="E380" s="7" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="F380" s="7" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="G380" s="7" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="H380" s="8" t="s">
         <v>21</v>
@@ -18486,22 +18491,22 @@
         <v>374.0</v>
       </c>
       <c r="B381" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C381" s="7" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="D381" s="7" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="E381" s="7" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="F381" s="7" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="G381" s="7" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="H381" s="8" t="s">
         <v>21</v>
@@ -18512,22 +18517,22 @@
         <v>375.0</v>
       </c>
       <c r="B382" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C382" s="7" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="D382" s="7" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="E382" s="7" t="s">
         <v>107</v>
       </c>
       <c r="F382" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="G382" s="7" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="H382" s="8" t="s">
         <v>15</v>
@@ -18538,22 +18543,22 @@
         <v>376.0</v>
       </c>
       <c r="B383" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C383" s="7" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="D383" s="7" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="E383" s="7" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="F383" s="7" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="G383" s="7" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="H383" s="8" t="s">
         <v>38</v>
@@ -18564,22 +18569,22 @@
         <v>377.0</v>
       </c>
       <c r="B384" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C384" s="7" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="D384" s="7" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="E384" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="F384" s="7" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="G384" s="7" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="H384" s="8" t="s">
         <v>38</v>
@@ -18590,13 +18595,13 @@
         <v>378.0</v>
       </c>
       <c r="B385" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C385" s="7" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="D385" s="7" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="E385" s="7" t="s">
         <v>671</v>
@@ -18616,22 +18621,22 @@
         <v>379.0</v>
       </c>
       <c r="B386" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C386" s="7" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="D386" s="7" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="E386" s="7" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="F386" s="7" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="G386" s="7" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H386" s="8" t="s">
         <v>27</v>
@@ -18642,10 +18647,10 @@
         <v>380.0</v>
       </c>
       <c r="B387" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C387" s="7" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="D387" s="7" t="b">
         <v>1</v>
@@ -18664,22 +18669,22 @@
         <v>381.0</v>
       </c>
       <c r="B388" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C388" s="7" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="D388" s="7" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="E388" s="7" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="F388" s="7" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="G388" s="7" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H388" s="8" t="s">
         <v>21</v>
@@ -18690,10 +18695,10 @@
         <v>382.0</v>
       </c>
       <c r="B389" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C389" s="7" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="D389" s="7" t="s">
         <v>835</v>
@@ -18705,7 +18710,7 @@
         <v>139</v>
       </c>
       <c r="G389" s="7" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="H389" s="8" t="s">
         <v>15</v>
@@ -18716,22 +18721,22 @@
         <v>383.0</v>
       </c>
       <c r="B390" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C390" s="7" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="D390" s="7" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="E390" s="7" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="F390" s="7" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="G390" s="7" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="H390" s="8" t="s">
         <v>15</v>
@@ -18742,16 +18747,16 @@
         <v>384.0</v>
       </c>
       <c r="B391" s="9" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C391" s="10" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="D391" s="10" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="E391" s="10" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="F391" s="10"/>
       <c r="G391" s="10"/>
@@ -18764,22 +18769,22 @@
         <v>385.0</v>
       </c>
       <c r="B392" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C392" s="7" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="D392" s="7" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="E392" s="7" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="F392" s="7" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="G392" s="7" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="H392" s="8" t="s">
         <v>21</v>
@@ -18790,22 +18795,22 @@
         <v>386.0</v>
       </c>
       <c r="B393" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C393" s="7" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="D393" s="7" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="E393" s="7" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="F393" s="7" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="G393" s="7" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="H393" s="8" t="s">
         <v>15</v>
@@ -18816,22 +18821,22 @@
         <v>387.0</v>
       </c>
       <c r="B394" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C394" s="7" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="D394" s="7" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="E394" s="7" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="F394" s="7" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="G394" s="7" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="H394" s="8" t="s">
         <v>21</v>
@@ -18842,22 +18847,22 @@
         <v>388.0</v>
       </c>
       <c r="B395" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C395" s="7" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="D395" s="7" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="E395" s="7" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="F395" s="7" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="G395" s="7" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="H395" s="8" t="s">
         <v>15</v>
@@ -18868,22 +18873,22 @@
         <v>389.0</v>
       </c>
       <c r="B396" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C396" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="D396" s="7" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="E396" s="7" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="F396" s="7" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="G396" s="7" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="H396" s="8" t="s">
         <v>27</v>
@@ -18894,22 +18899,22 @@
         <v>390.0</v>
       </c>
       <c r="B397" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C397" s="7" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="D397" s="7" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="E397" s="7" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="F397" s="7" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="G397" s="7" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="H397" s="8" t="s">
         <v>27</v>
@@ -18920,22 +18925,22 @@
         <v>391.0</v>
       </c>
       <c r="B398" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C398" s="7" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="D398" s="7" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="E398" s="7" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="F398" s="7" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="G398" s="7" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="H398" s="8" t="s">
         <v>27</v>
@@ -18946,10 +18951,10 @@
         <v>392.0</v>
       </c>
       <c r="B399" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C399" s="7" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="D399" s="12" t="s">
         <v>257</v>
@@ -18958,10 +18963,10 @@
         <v>259</v>
       </c>
       <c r="F399" s="7" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="G399" s="7" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="H399" s="8" t="s">
         <v>21</v>
@@ -18972,10 +18977,10 @@
         <v>393.0</v>
       </c>
       <c r="B400" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C400" s="7" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="D400" s="7" t="b">
         <v>1</v>
@@ -18994,13 +18999,13 @@
         <v>394.0</v>
       </c>
       <c r="B401" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C401" s="7" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="D401" s="7" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="E401" s="7" t="s">
         <v>671</v>
@@ -19020,22 +19025,22 @@
         <v>395.0</v>
       </c>
       <c r="B402" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C402" s="7" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="D402" s="7" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="E402" s="7" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="F402" s="7" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="G402" s="7" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="H402" s="8" t="s">
         <v>21</v>
@@ -19046,10 +19051,10 @@
         <v>396.0</v>
       </c>
       <c r="B403" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C403" s="7" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="D403" s="7" t="s">
         <v>835</v>
@@ -19061,7 +19066,7 @@
         <v>105</v>
       </c>
       <c r="G403" s="7" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="H403" s="8" t="s">
         <v>15</v>
@@ -19072,22 +19077,22 @@
         <v>397.0</v>
       </c>
       <c r="B404" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C404" s="7" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="D404" s="7" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="E404" s="7" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="F404" s="7" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="G404" s="7" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="H404" s="8" t="s">
         <v>38</v>
@@ -19098,22 +19103,22 @@
         <v>398.0</v>
       </c>
       <c r="B405" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C405" s="7" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="D405" s="7" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="E405" s="7" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="F405" s="7" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="G405" s="7" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="H405" s="8" t="s">
         <v>21</v>
@@ -19124,13 +19129,13 @@
         <v>399.0</v>
       </c>
       <c r="B406" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C406" s="7" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="D406" s="13" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="E406" s="7" t="s">
         <v>850</v>
@@ -19150,22 +19155,22 @@
         <v>400.0</v>
       </c>
       <c r="B407" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C407" s="7" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="D407" s="7" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="E407" s="7" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="F407" s="7" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="G407" s="7" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="H407" s="8" t="s">
         <v>38</v>
@@ -19176,19 +19181,19 @@
         <v>401.0</v>
       </c>
       <c r="B408" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C408" s="7" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="D408" s="7" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="E408" s="7" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="F408" s="7" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="G408" s="7" t="s">
         <v>492</v>
@@ -19202,22 +19207,22 @@
         <v>402.0</v>
       </c>
       <c r="B409" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C409" s="7" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="D409" s="7" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="E409" s="7" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="F409" s="7" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="G409" s="7" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="H409" s="8" t="s">
         <v>38</v>
@@ -19228,22 +19233,22 @@
         <v>403.0</v>
       </c>
       <c r="B410" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C410" s="7" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="D410" s="7" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="E410" s="7" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="F410" s="7" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G410" s="7" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="H410" s="8" t="s">
         <v>27</v>
@@ -19254,10 +19259,10 @@
         <v>404.0</v>
       </c>
       <c r="B411" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C411" s="7" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="D411" s="7">
         <v>3.0</v>
@@ -19280,22 +19285,22 @@
         <v>405.0</v>
       </c>
       <c r="B412" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C412" s="7" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="D412" s="7" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="E412" s="7" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="F412" s="7" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G412" s="7" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="H412" s="8" t="s">
         <v>27</v>
@@ -19306,22 +19311,22 @@
         <v>406.0</v>
       </c>
       <c r="B413" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C413" s="7" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="D413" s="7" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="E413" s="7" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="F413" s="7" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="G413" s="7" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="H413" s="8" t="s">
         <v>15</v>
@@ -19332,10 +19337,10 @@
         <v>407.0</v>
       </c>
       <c r="B414" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C414" s="7" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="D414" s="7" t="s">
         <v>835</v>
@@ -19347,7 +19352,7 @@
         <v>107</v>
       </c>
       <c r="G414" s="7" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="H414" s="8" t="s">
         <v>21</v>
@@ -19358,22 +19363,22 @@
         <v>408.0</v>
       </c>
       <c r="B415" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C415" s="7" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="D415" s="7" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="E415" s="7" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="F415" s="7" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G415" s="7" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H415" s="8" t="s">
         <v>27</v>
@@ -19384,22 +19389,22 @@
         <v>409.0</v>
       </c>
       <c r="B416" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C416" s="7" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D416" s="7" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E416" s="7" t="s">
         <v>1710</v>
       </c>
-      <c r="D416" s="7" t="s">
+      <c r="F416" s="7" t="s">
         <v>1708</v>
       </c>
-      <c r="E416" s="7" t="s">
-        <v>1709</v>
-      </c>
-      <c r="F416" s="7" t="s">
+      <c r="G416" s="7" t="s">
         <v>1707</v>
-      </c>
-      <c r="G416" s="7" t="s">
-        <v>1706</v>
       </c>
       <c r="H416" s="8" t="s">
         <v>21</v>
@@ -19410,22 +19415,22 @@
         <v>410.0</v>
       </c>
       <c r="B417" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C417" s="7" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="D417" s="7" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="E417" s="7" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="F417" s="7" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="G417" s="7" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="H417" s="8" t="s">
         <v>38</v>
@@ -19436,22 +19441,22 @@
         <v>411.0</v>
       </c>
       <c r="B418" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C418" s="7" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="D418" s="7" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="E418" s="7" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="F418" s="7" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="G418" s="7" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="H418" s="8" t="s">
         <v>38</v>
@@ -19462,22 +19467,22 @@
         <v>412.0</v>
       </c>
       <c r="B419" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C419" s="7" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="D419" s="7" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="E419" s="7" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="F419" s="7" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G419" s="7" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H419" s="8" t="s">
         <v>27</v>
@@ -19488,22 +19493,22 @@
         <v>413.0</v>
       </c>
       <c r="B420" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C420" s="7" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="D420" s="7" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="E420" s="7" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="F420" s="7" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G420" s="7" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="H420" s="8" t="s">
         <v>38</v>
@@ -19514,22 +19519,22 @@
         <v>414.0</v>
       </c>
       <c r="B421" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C421" s="7" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="D421" s="7" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="E421" s="7" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="F421" s="7" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G421" s="7" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="H421" s="8" t="s">
         <v>15</v>
@@ -19540,22 +19545,22 @@
         <v>415.0</v>
       </c>
       <c r="B422" s="9" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C422" s="10" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="D422" s="10" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="E422" s="10" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="F422" s="10" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="G422" s="10" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="H422" s="11" t="s">
         <v>21</v>
@@ -19566,19 +19571,19 @@
         <v>416.0</v>
       </c>
       <c r="B423" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C423" s="7" t="s">
-        <v>1741</v>
-      </c>
-      <c r="D423" s="14" t="s">
         <v>1742</v>
       </c>
+      <c r="D423" s="15" t="s">
+        <v>1743</v>
+      </c>
       <c r="E423" s="7" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="F423" s="7" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G423" s="7" t="s">
         <v>851</v>
@@ -19592,22 +19597,22 @@
         <v>417.0</v>
       </c>
       <c r="B424" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C424" s="7" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="D424" s="7" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="E424" s="7" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="F424" s="7" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="G424" s="7" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="H424" s="8" t="s">
         <v>27</v>
@@ -19618,22 +19623,22 @@
         <v>418.0</v>
       </c>
       <c r="B425" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C425" s="7" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="D425" s="7" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="E425" s="7" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="F425" s="7" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="G425" s="7" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="H425" s="8" t="s">
         <v>27</v>
@@ -19644,22 +19649,22 @@
         <v>419.0</v>
       </c>
       <c r="B426" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C426" s="7" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="D426" s="7" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="E426" s="7" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="F426" s="7" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="G426" s="7" t="s">
-        <v>1757</v>
+        <v>51</v>
       </c>
       <c r="H426" s="8" t="s">
         <v>15</v>
@@ -19670,22 +19675,22 @@
         <v>420.0</v>
       </c>
       <c r="B427" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C427" s="7" t="s">
         <v>1758</v>
       </c>
       <c r="D427" s="7" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="E427" s="7" t="s">
         <v>1759</v>
       </c>
       <c r="F427" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G427" s="7" t="s">
         <v>1757</v>
-      </c>
-      <c r="G427" s="7" t="s">
-        <v>1756</v>
       </c>
       <c r="H427" s="8" t="s">
         <v>15</v>
@@ -19696,7 +19701,7 @@
         <v>421.0</v>
       </c>
       <c r="B428" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C428" s="7" t="s">
         <v>1760</v>
@@ -19722,7 +19727,7 @@
         <v>422.0</v>
       </c>
       <c r="B429" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C429" s="7" t="s">
         <v>1765</v>
@@ -19748,7 +19753,7 @@
         <v>423.0</v>
       </c>
       <c r="B430" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C430" s="7" t="s">
         <v>1770</v>
@@ -19774,7 +19779,7 @@
         <v>424.0</v>
       </c>
       <c r="B431" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C431" s="7" t="s">
         <v>1775</v>
@@ -19800,7 +19805,7 @@
         <v>425.0</v>
       </c>
       <c r="B432" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C432" s="7" t="s">
         <v>1780</v>
@@ -19826,7 +19831,7 @@
         <v>426.0</v>
       </c>
       <c r="B433" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C433" s="7" t="s">
         <v>1785</v>
@@ -19852,7 +19857,7 @@
         <v>427.0</v>
       </c>
       <c r="B434" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C434" s="7" t="s">
         <v>1790</v>
@@ -19878,7 +19883,7 @@
         <v>428.0</v>
       </c>
       <c r="B435" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C435" s="7" t="s">
         <v>1791</v>
@@ -19900,7 +19905,7 @@
         <v>429.0</v>
       </c>
       <c r="B436" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C436" s="7" t="s">
         <v>1792</v>
@@ -19926,7 +19931,7 @@
         <v>430.0</v>
       </c>
       <c r="B437" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C437" s="7" t="s">
         <v>1797</v>
@@ -19938,7 +19943,7 @@
         <v>492</v>
       </c>
       <c r="F437" s="7" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="G437" s="7" t="s">
         <v>1799</v>
@@ -20184,10 +20189,10 @@
         <v>1840</v>
       </c>
       <c r="F447" s="7" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="G447" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H447" s="8" t="s">
         <v>38</v>
@@ -20577,7 +20582,7 @@
         <v>1905</v>
       </c>
       <c r="G462" s="7" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H462" s="8" t="s">
         <v>15</v>
@@ -20681,7 +20686,7 @@
         <v>1924</v>
       </c>
       <c r="G466" s="7" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H466" s="8" t="s">
         <v>15</v>
@@ -21403,7 +21408,7 @@
         <v>2027</v>
       </c>
       <c r="E494" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="F494" s="7" t="s">
         <v>2028</v>
@@ -21958,7 +21963,7 @@
         <v>2090</v>
       </c>
       <c r="H515" s="8" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="516">
@@ -21981,7 +21986,7 @@
         <v>1904</v>
       </c>
       <c r="G516" s="7" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H516" s="8" t="s">
         <v>15</v>
@@ -22608,7 +22613,7 @@
         <v>2193</v>
       </c>
       <c r="D541" s="7" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="E541" s="7" t="s">
         <v>2194</v>
@@ -22666,7 +22671,7 @@
         <v>2200</v>
       </c>
       <c r="F543" s="7" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="G543" s="7" t="s">
         <v>2201</v>
@@ -22744,7 +22749,7 @@
         <v>2200</v>
       </c>
       <c r="F546" s="7" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="G546" s="7" t="s">
         <v>2201</v>
@@ -22796,7 +22801,7 @@
         <v>2215</v>
       </c>
       <c r="F548" s="7" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="G548" s="7" t="s">
         <v>2200</v>
@@ -22877,7 +22882,7 @@
         <v>2219</v>
       </c>
       <c r="G551" s="7" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H551" s="8" t="s">
         <v>15</v>
@@ -22975,7 +22980,7 @@
         <v>2200</v>
       </c>
       <c r="E555" s="7" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="F555" s="7" t="s">
         <v>2201</v>
@@ -23839,7 +23844,7 @@
         <v>2184</v>
       </c>
       <c r="G588" s="7" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="H588" s="8" t="s">
         <v>15</v>
@@ -24506,7 +24511,7 @@
         <v>2495</v>
       </c>
       <c r="D614" s="7" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="E614" s="7" t="s">
         <v>2496</v>
@@ -24876,7 +24881,7 @@
         <v>2556</v>
       </c>
       <c r="F628" s="7" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="G628" s="7" t="s">
         <v>2557</v>
@@ -25009,7 +25014,7 @@
         <v>2579</v>
       </c>
       <c r="G633" s="7" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="H633" s="8" t="s">
         <v>38</v>
@@ -25061,7 +25066,7 @@
         <v>2588</v>
       </c>
       <c r="G635" s="7" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="H635" s="8" t="s">
         <v>27</v>
@@ -25113,7 +25118,7 @@
         <v>2596</v>
       </c>
       <c r="G637" s="7" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="H637" s="8" t="s">
         <v>38</v>
@@ -25145,13 +25150,13 @@
         <v>2600</v>
       </c>
       <c r="E639" s="7" t="s">
+        <v>2197</v>
+      </c>
+      <c r="F639" s="7" t="s">
         <v>2601</v>
       </c>
-      <c r="F639" s="7" t="s">
+      <c r="G639" s="7" t="s">
         <v>2602</v>
-      </c>
-      <c r="G639" s="7" t="s">
-        <v>2603</v>
       </c>
       <c r="H639" s="8" t="s">
         <v>21</v>
@@ -25165,19 +25170,19 @@
         <v>2598</v>
       </c>
       <c r="C640" s="7" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D640" s="7" t="s">
         <v>2604</v>
       </c>
-      <c r="D640" s="7" t="s">
+      <c r="E640" s="7" t="s">
         <v>2605</v>
       </c>
-      <c r="E640" s="7" t="s">
+      <c r="F640" s="7" t="s">
         <v>2606</v>
       </c>
-      <c r="F640" s="7" t="s">
+      <c r="G640" s="7" t="s">
         <v>2607</v>
-      </c>
-      <c r="G640" s="7" t="s">
-        <v>2608</v>
       </c>
       <c r="H640" s="8" t="s">
         <v>27</v>
@@ -25191,19 +25196,19 @@
         <v>2598</v>
       </c>
       <c r="C641" s="7" t="s">
+        <v>2608</v>
+      </c>
+      <c r="D641" s="7" t="s">
         <v>2609</v>
       </c>
-      <c r="D641" s="7" t="s">
+      <c r="E641" s="7" t="s">
         <v>2610</v>
       </c>
-      <c r="E641" s="7" t="s">
+      <c r="F641" s="7" t="s">
         <v>2611</v>
       </c>
-      <c r="F641" s="7" t="s">
+      <c r="G641" s="7" t="s">
         <v>2612</v>
-      </c>
-      <c r="G641" s="7" t="s">
-        <v>2613</v>
       </c>
       <c r="H641" s="8" t="s">
         <v>27</v>
@@ -25217,19 +25222,19 @@
         <v>2598</v>
       </c>
       <c r="C642" s="7" t="s">
+        <v>2613</v>
+      </c>
+      <c r="D642" s="7" t="s">
         <v>2614</v>
       </c>
-      <c r="D642" s="7" t="s">
+      <c r="E642" s="7" t="s">
         <v>2615</v>
       </c>
-      <c r="E642" s="7" t="s">
+      <c r="F642" s="7" t="s">
         <v>2616</v>
       </c>
-      <c r="F642" s="7" t="s">
+      <c r="G642" s="7" t="s">
         <v>2617</v>
-      </c>
-      <c r="G642" s="7" t="s">
-        <v>2618</v>
       </c>
       <c r="H642" s="8" t="s">
         <v>15</v>
@@ -25243,19 +25248,19 @@
         <v>2598</v>
       </c>
       <c r="C643" s="7" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="D643" s="7" t="s">
         <v>1960</v>
       </c>
       <c r="E643" s="7" t="s">
+        <v>2619</v>
+      </c>
+      <c r="F643" s="7" t="s">
         <v>2620</v>
       </c>
-      <c r="F643" s="7" t="s">
+      <c r="G643" s="7" t="s">
         <v>2621</v>
-      </c>
-      <c r="G643" s="7" t="s">
-        <v>2622</v>
       </c>
       <c r="H643" s="8" t="s">
         <v>27</v>
@@ -25269,16 +25274,16 @@
         <v>2598</v>
       </c>
       <c r="C644" s="7" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="D644" s="7" t="s">
         <v>1960</v>
       </c>
       <c r="E644" s="7" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="F644" s="7" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="G644" s="7" t="s">
         <v>2544</v>
@@ -25295,19 +25300,19 @@
         <v>2598</v>
       </c>
       <c r="C645" s="7" t="s">
+        <v>2623</v>
+      </c>
+      <c r="D645" s="7" t="s">
         <v>2624</v>
       </c>
-      <c r="D645" s="7" t="s">
+      <c r="E645" s="7" t="s">
         <v>2625</v>
       </c>
-      <c r="E645" s="7" t="s">
+      <c r="F645" s="7" t="s">
         <v>2626</v>
       </c>
-      <c r="F645" s="7" t="s">
+      <c r="G645" s="7" t="s">
         <v>2627</v>
-      </c>
-      <c r="G645" s="7" t="s">
-        <v>2628</v>
       </c>
       <c r="H645" s="8" t="s">
         <v>27</v>
@@ -25321,19 +25326,19 @@
         <v>2598</v>
       </c>
       <c r="C646" s="7" t="s">
+        <v>2628</v>
+      </c>
+      <c r="D646" s="7" t="s">
         <v>2629</v>
       </c>
-      <c r="D646" s="7" t="s">
+      <c r="E646" s="7" t="s">
         <v>2630</v>
       </c>
-      <c r="E646" s="7" t="s">
+      <c r="F646" s="7" t="s">
         <v>2631</v>
       </c>
-      <c r="F646" s="7" t="s">
+      <c r="G646" s="7" t="s">
         <v>2632</v>
-      </c>
-      <c r="G646" s="7" t="s">
-        <v>2633</v>
       </c>
       <c r="H646" s="8" t="s">
         <v>15</v>
@@ -25347,19 +25352,19 @@
         <v>2598</v>
       </c>
       <c r="C647" s="7" t="s">
+        <v>2633</v>
+      </c>
+      <c r="D647" s="7" t="s">
         <v>2634</v>
       </c>
-      <c r="D647" s="7" t="s">
+      <c r="E647" s="7" t="s">
         <v>2635</v>
       </c>
-      <c r="E647" s="7" t="s">
+      <c r="F647" s="7" t="s">
         <v>2636</v>
       </c>
-      <c r="F647" s="7" t="s">
+      <c r="G647" s="7" t="s">
         <v>2637</v>
-      </c>
-      <c r="G647" s="7" t="s">
-        <v>2638</v>
       </c>
       <c r="H647" s="8" t="s">
         <v>27</v>
@@ -25373,19 +25378,19 @@
         <v>2598</v>
       </c>
       <c r="C648" s="7" t="s">
+        <v>2638</v>
+      </c>
+      <c r="D648" s="7" t="s">
         <v>2639</v>
       </c>
-      <c r="D648" s="7" t="s">
+      <c r="E648" s="7" t="s">
         <v>2640</v>
       </c>
-      <c r="E648" s="7" t="s">
+      <c r="F648" s="7" t="s">
         <v>2641</v>
       </c>
-      <c r="F648" s="7" t="s">
+      <c r="G648" s="7" t="s">
         <v>2642</v>
-      </c>
-      <c r="G648" s="7" t="s">
-        <v>2643</v>
       </c>
       <c r="H648" s="8" t="s">
         <v>15</v>
@@ -25399,7 +25404,7 @@
         <v>2598</v>
       </c>
       <c r="C649" s="7" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="D649" s="7">
         <v>2005.0</v>
@@ -25425,19 +25430,19 @@
         <v>2598</v>
       </c>
       <c r="C650" s="7" t="s">
+        <v>2644</v>
+      </c>
+      <c r="D650" s="7" t="s">
         <v>2645</v>
       </c>
-      <c r="D650" s="7" t="s">
+      <c r="E650" s="7" t="s">
         <v>2646</v>
       </c>
-      <c r="E650" s="7" t="s">
+      <c r="F650" s="7" t="s">
         <v>2647</v>
       </c>
-      <c r="F650" s="7" t="s">
+      <c r="G650" s="7" t="s">
         <v>2648</v>
-      </c>
-      <c r="G650" s="7" t="s">
-        <v>2649</v>
       </c>
       <c r="H650" s="8" t="s">
         <v>27</v>
@@ -25451,7 +25456,7 @@
         <v>2598</v>
       </c>
       <c r="C651" s="7" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="D651" s="7">
         <v>2008.0</v>
@@ -25477,19 +25482,19 @@
         <v>2598</v>
       </c>
       <c r="C652" s="7" t="s">
+        <v>2650</v>
+      </c>
+      <c r="D652" s="7" t="s">
         <v>2651</v>
       </c>
-      <c r="D652" s="7" t="s">
+      <c r="E652" s="7" t="s">
         <v>2652</v>
       </c>
-      <c r="E652" s="7" t="s">
+      <c r="F652" s="7" t="s">
         <v>2653</v>
       </c>
-      <c r="F652" s="7" t="s">
+      <c r="G652" s="7" t="s">
         <v>2654</v>
-      </c>
-      <c r="G652" s="7" t="s">
-        <v>2655</v>
       </c>
       <c r="H652" s="8" t="s">
         <v>15</v>
@@ -25503,19 +25508,19 @@
         <v>2598</v>
       </c>
       <c r="C653" s="7" t="s">
+        <v>2655</v>
+      </c>
+      <c r="D653" s="7" t="s">
         <v>2656</v>
       </c>
-      <c r="D653" s="7" t="s">
+      <c r="E653" s="7" t="s">
         <v>2657</v>
       </c>
-      <c r="E653" s="7" t="s">
+      <c r="F653" s="7" t="s">
         <v>2658</v>
       </c>
-      <c r="F653" s="7" t="s">
+      <c r="G653" s="7" t="s">
         <v>2659</v>
-      </c>
-      <c r="G653" s="7" t="s">
-        <v>2660</v>
       </c>
       <c r="H653" s="8" t="s">
         <v>27</v>
@@ -25529,19 +25534,19 @@
         <v>2598</v>
       </c>
       <c r="C654" s="7" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D654" s="7" t="s">
         <v>2661</v>
       </c>
-      <c r="D654" s="7" t="s">
+      <c r="E654" s="7" t="s">
         <v>2662</v>
       </c>
-      <c r="E654" s="7" t="s">
+      <c r="F654" s="7" t="s">
         <v>2663</v>
       </c>
-      <c r="F654" s="7" t="s">
+      <c r="G654" s="7" t="s">
         <v>2664</v>
-      </c>
-      <c r="G654" s="7" t="s">
-        <v>2665</v>
       </c>
       <c r="H654" s="8" t="s">
         <v>27</v>
@@ -25555,19 +25560,19 @@
         <v>2598</v>
       </c>
       <c r="C655" s="7" t="s">
+        <v>2665</v>
+      </c>
+      <c r="D655" s="7" t="s">
         <v>2666</v>
-      </c>
-      <c r="D655" s="7" t="s">
-        <v>2667</v>
       </c>
       <c r="E655" s="7" t="s">
         <v>1961</v>
       </c>
       <c r="F655" s="7" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="G655" s="7" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="H655" s="8" t="s">
         <v>15</v>
@@ -25581,16 +25586,16 @@
         <v>2598</v>
       </c>
       <c r="C656" s="7" t="s">
+        <v>2668</v>
+      </c>
+      <c r="D656" s="7" t="s">
         <v>2669</v>
       </c>
-      <c r="D656" s="7" t="s">
+      <c r="E656" s="7" t="s">
         <v>2670</v>
       </c>
-      <c r="E656" s="7" t="s">
+      <c r="F656" s="7" t="s">
         <v>2671</v>
-      </c>
-      <c r="F656" s="7" t="s">
-        <v>2672</v>
       </c>
       <c r="G656" s="7" t="s">
         <v>1961</v>
@@ -25607,19 +25612,19 @@
         <v>2598</v>
       </c>
       <c r="C657" s="7" t="s">
+        <v>2672</v>
+      </c>
+      <c r="D657" s="7" t="s">
         <v>2673</v>
       </c>
-      <c r="D657" s="7" t="s">
+      <c r="E657" s="7" t="s">
         <v>2674</v>
       </c>
-      <c r="E657" s="7" t="s">
+      <c r="F657" s="7" t="s">
         <v>2675</v>
       </c>
-      <c r="F657" s="7" t="s">
+      <c r="G657" s="7" t="s">
         <v>2676</v>
-      </c>
-      <c r="G657" s="7" t="s">
-        <v>2677</v>
       </c>
       <c r="H657" s="8" t="s">
         <v>27</v>
@@ -25633,19 +25638,19 @@
         <v>2598</v>
       </c>
       <c r="C658" s="7" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="D658" s="7" t="s">
         <v>1769</v>
       </c>
       <c r="E658" s="7" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
       <c r="F658" s="7" t="s">
         <v>223</v>
       </c>
       <c r="G658" s="7" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H658" s="8" t="s">
         <v>38</v>
@@ -25659,19 +25664,19 @@
         <v>2598</v>
       </c>
       <c r="C659" s="7" t="s">
+        <v>2679</v>
+      </c>
+      <c r="D659" s="7" t="s">
         <v>2680</v>
       </c>
-      <c r="D659" s="7" t="s">
+      <c r="E659" s="7" t="s">
         <v>2681</v>
       </c>
-      <c r="E659" s="7" t="s">
+      <c r="F659" s="7" t="s">
         <v>2682</v>
       </c>
-      <c r="F659" s="7" t="s">
+      <c r="G659" s="7" t="s">
         <v>2683</v>
-      </c>
-      <c r="G659" s="7" t="s">
-        <v>2684</v>
       </c>
       <c r="H659" s="8" t="s">
         <v>38</v>
@@ -25685,19 +25690,19 @@
         <v>2598</v>
       </c>
       <c r="C660" s="7" t="s">
+        <v>2684</v>
+      </c>
+      <c r="D660" s="7" t="s">
         <v>2685</v>
       </c>
-      <c r="D660" s="7" t="s">
+      <c r="E660" s="7" t="s">
         <v>2686</v>
       </c>
-      <c r="E660" s="7" t="s">
+      <c r="F660" s="7" t="s">
         <v>2687</v>
       </c>
-      <c r="F660" s="7" t="s">
+      <c r="G660" s="7" t="s">
         <v>2688</v>
-      </c>
-      <c r="G660" s="7" t="s">
-        <v>2689</v>
       </c>
       <c r="H660" s="8" t="s">
         <v>27</v>
@@ -25711,19 +25716,19 @@
         <v>2598</v>
       </c>
       <c r="C661" s="7" t="s">
+        <v>2689</v>
+      </c>
+      <c r="D661" s="7" t="s">
         <v>2690</v>
       </c>
-      <c r="D661" s="7" t="s">
+      <c r="E661" s="7" t="s">
         <v>2691</v>
       </c>
-      <c r="E661" s="7" t="s">
+      <c r="F661" s="7" t="s">
         <v>2692</v>
       </c>
-      <c r="F661" s="7" t="s">
+      <c r="G661" s="7" t="s">
         <v>2693</v>
-      </c>
-      <c r="G661" s="7" t="s">
-        <v>2694</v>
       </c>
       <c r="H661" s="8" t="s">
         <v>15</v>
@@ -25737,19 +25742,19 @@
         <v>2598</v>
       </c>
       <c r="C662" s="7" t="s">
+        <v>2694</v>
+      </c>
+      <c r="D662" s="7" t="s">
         <v>2695</v>
       </c>
-      <c r="D662" s="7" t="s">
+      <c r="E662" s="7" t="s">
         <v>2696</v>
       </c>
-      <c r="E662" s="7" t="s">
+      <c r="F662" s="7" t="s">
         <v>2697</v>
       </c>
-      <c r="F662" s="7" t="s">
+      <c r="G662" s="7" t="s">
         <v>2698</v>
-      </c>
-      <c r="G662" s="7" t="s">
-        <v>2699</v>
       </c>
       <c r="H662" s="8" t="s">
         <v>15</v>
@@ -25763,19 +25768,19 @@
         <v>2598</v>
       </c>
       <c r="C663" s="7" t="s">
+        <v>2699</v>
+      </c>
+      <c r="D663" s="7" t="s">
         <v>2700</v>
       </c>
-      <c r="D663" s="7" t="s">
+      <c r="E663" s="7" t="s">
         <v>2701</v>
       </c>
-      <c r="E663" s="7" t="s">
+      <c r="F663" s="7" t="s">
         <v>2702</v>
       </c>
-      <c r="F663" s="7" t="s">
+      <c r="G663" s="7" t="s">
         <v>2703</v>
-      </c>
-      <c r="G663" s="7" t="s">
-        <v>2704</v>
       </c>
       <c r="H663" s="8" t="s">
         <v>15</v>
@@ -25789,19 +25794,19 @@
         <v>2598</v>
       </c>
       <c r="C664" s="7" t="s">
+        <v>2704</v>
+      </c>
+      <c r="D664" s="7" t="s">
         <v>2705</v>
       </c>
-      <c r="D664" s="7" t="s">
+      <c r="E664" s="7" t="s">
         <v>2706</v>
       </c>
-      <c r="E664" s="7" t="s">
-        <v>2707</v>
-      </c>
       <c r="F664" s="7" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
       <c r="G664" s="7" t="s">
-        <v>2694</v>
+        <v>2693</v>
       </c>
       <c r="H664" s="8" t="s">
         <v>27</v>
@@ -25815,19 +25820,19 @@
         <v>2598</v>
       </c>
       <c r="C665" s="7" t="s">
+        <v>2707</v>
+      </c>
+      <c r="D665" s="7" t="s">
         <v>2708</v>
       </c>
-      <c r="D665" s="7" t="s">
+      <c r="E665" s="7" t="s">
         <v>2709</v>
       </c>
-      <c r="E665" s="7" t="s">
+      <c r="F665" s="7" t="s">
         <v>2710</v>
       </c>
-      <c r="F665" s="7" t="s">
+      <c r="G665" s="7" t="s">
         <v>2711</v>
-      </c>
-      <c r="G665" s="7" t="s">
-        <v>2712</v>
       </c>
       <c r="H665" s="8" t="s">
         <v>38</v>
@@ -25841,19 +25846,19 @@
         <v>2598</v>
       </c>
       <c r="C666" s="7" t="s">
+        <v>2712</v>
+      </c>
+      <c r="D666" s="7" t="s">
         <v>2713</v>
       </c>
-      <c r="D666" s="7" t="s">
+      <c r="E666" s="7" t="s">
         <v>2714</v>
       </c>
-      <c r="E666" s="7" t="s">
+      <c r="F666" s="7" t="s">
         <v>2715</v>
       </c>
-      <c r="F666" s="7" t="s">
+      <c r="G666" s="7" t="s">
         <v>2716</v>
-      </c>
-      <c r="G666" s="7" t="s">
-        <v>2717</v>
       </c>
       <c r="H666" s="8" t="s">
         <v>27</v>
@@ -25867,19 +25872,19 @@
         <v>2598</v>
       </c>
       <c r="C667" s="7" t="s">
+        <v>2717</v>
+      </c>
+      <c r="D667" s="7" t="s">
         <v>2718</v>
       </c>
-      <c r="D667" s="7" t="s">
+      <c r="E667" s="7" t="s">
         <v>2719</v>
       </c>
-      <c r="E667" s="7" t="s">
+      <c r="F667" s="7" t="s">
         <v>2720</v>
       </c>
-      <c r="F667" s="7" t="s">
-        <v>2721</v>
-      </c>
       <c r="G667" s="7" t="s">
-        <v>2694</v>
+        <v>2693</v>
       </c>
       <c r="H667" s="8" t="s">
         <v>27</v>
@@ -25893,19 +25898,19 @@
         <v>2598</v>
       </c>
       <c r="C668" s="7" t="s">
+        <v>2721</v>
+      </c>
+      <c r="D668" s="7" t="s">
         <v>2722</v>
       </c>
-      <c r="D668" s="7" t="s">
+      <c r="E668" s="7" t="s">
         <v>2723</v>
       </c>
-      <c r="E668" s="7" t="s">
+      <c r="F668" s="7" t="s">
         <v>2724</v>
       </c>
-      <c r="F668" s="7" t="s">
+      <c r="G668" s="7" t="s">
         <v>2725</v>
-      </c>
-      <c r="G668" s="7" t="s">
-        <v>2726</v>
       </c>
       <c r="H668" s="8" t="s">
         <v>15</v>
@@ -25919,19 +25924,19 @@
         <v>2598</v>
       </c>
       <c r="C669" s="7" t="s">
+        <v>2726</v>
+      </c>
+      <c r="D669" s="7" t="s">
         <v>2727</v>
       </c>
-      <c r="D669" s="7" t="s">
+      <c r="E669" s="7" t="s">
         <v>2728</v>
       </c>
-      <c r="E669" s="7" t="s">
+      <c r="F669" s="7" t="s">
         <v>2729</v>
       </c>
-      <c r="F669" s="7" t="s">
+      <c r="G669" s="7" t="s">
         <v>2730</v>
-      </c>
-      <c r="G669" s="7" t="s">
-        <v>2731</v>
       </c>
       <c r="H669" s="8" t="s">
         <v>15</v>
@@ -25945,19 +25950,19 @@
         <v>2598</v>
       </c>
       <c r="C670" s="7" t="s">
+        <v>2731</v>
+      </c>
+      <c r="D670" s="7" t="s">
         <v>2732</v>
       </c>
-      <c r="D670" s="7" t="s">
+      <c r="E670" s="7" t="s">
         <v>2733</v>
       </c>
-      <c r="E670" s="7" t="s">
+      <c r="F670" s="7" t="s">
         <v>2734</v>
       </c>
-      <c r="F670" s="7" t="s">
+      <c r="G670" s="7" t="s">
         <v>2735</v>
-      </c>
-      <c r="G670" s="7" t="s">
-        <v>2736</v>
       </c>
       <c r="H670" s="8" t="s">
         <v>15</v>
@@ -25971,19 +25976,19 @@
         <v>2598</v>
       </c>
       <c r="C671" s="7" t="s">
+        <v>2736</v>
+      </c>
+      <c r="D671" s="7" t="s">
         <v>2737</v>
       </c>
-      <c r="D671" s="7" t="s">
+      <c r="E671" s="7" t="s">
         <v>2738</v>
       </c>
-      <c r="E671" s="7" t="s">
+      <c r="F671" s="7" t="s">
         <v>2739</v>
       </c>
-      <c r="F671" s="7" t="s">
+      <c r="G671" s="7" t="s">
         <v>2740</v>
-      </c>
-      <c r="G671" s="7" t="s">
-        <v>2741</v>
       </c>
       <c r="H671" s="8" t="s">
         <v>27</v>
@@ -25997,19 +26002,19 @@
         <v>2598</v>
       </c>
       <c r="C672" s="7" t="s">
+        <v>2741</v>
+      </c>
+      <c r="D672" s="7" t="s">
+        <v>2729</v>
+      </c>
+      <c r="E672" s="7" t="s">
         <v>2742</v>
       </c>
-      <c r="D672" s="7" t="s">
-        <v>2730</v>
-      </c>
-      <c r="E672" s="7" t="s">
+      <c r="F672" s="7" t="s">
         <v>2743</v>
       </c>
-      <c r="F672" s="7" t="s">
+      <c r="G672" s="7" t="s">
         <v>2744</v>
-      </c>
-      <c r="G672" s="7" t="s">
-        <v>2745</v>
       </c>
       <c r="H672" s="8" t="s">
         <v>27</v>
@@ -26023,19 +26028,19 @@
         <v>2598</v>
       </c>
       <c r="C673" s="7" t="s">
+        <v>2745</v>
+      </c>
+      <c r="D673" s="7" t="s">
         <v>2746</v>
       </c>
-      <c r="D673" s="7" t="s">
+      <c r="E673" s="7" t="s">
         <v>2747</v>
       </c>
-      <c r="E673" s="7" t="s">
+      <c r="F673" s="7" t="s">
         <v>2748</v>
       </c>
-      <c r="F673" s="7" t="s">
+      <c r="G673" s="7" t="s">
         <v>2749</v>
-      </c>
-      <c r="G673" s="7" t="s">
-        <v>2750</v>
       </c>
       <c r="H673" s="8" t="s">
         <v>15</v>
@@ -26049,19 +26054,19 @@
         <v>2598</v>
       </c>
       <c r="C674" s="7" t="s">
+        <v>2750</v>
+      </c>
+      <c r="D674" s="7" t="s">
         <v>2751</v>
       </c>
-      <c r="D674" s="7" t="s">
+      <c r="E674" s="7" t="s">
         <v>2752</v>
       </c>
-      <c r="E674" s="7" t="s">
+      <c r="F674" s="7" t="s">
         <v>2753</v>
       </c>
-      <c r="F674" s="7" t="s">
+      <c r="G674" s="7" t="s">
         <v>2754</v>
-      </c>
-      <c r="G674" s="7" t="s">
-        <v>2755</v>
       </c>
       <c r="H674" s="8" t="s">
         <v>27</v>
@@ -26075,19 +26080,19 @@
         <v>2598</v>
       </c>
       <c r="C675" s="7" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="D675" s="7" t="s">
+        <v>2728</v>
+      </c>
+      <c r="E675" s="7" t="s">
+        <v>2730</v>
+      </c>
+      <c r="F675" s="7" t="s">
         <v>2729</v>
       </c>
-      <c r="E675" s="7" t="s">
-        <v>2731</v>
-      </c>
-      <c r="F675" s="7" t="s">
-        <v>2730</v>
-      </c>
       <c r="G675" s="7" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="H675" s="8" t="s">
         <v>38</v>
@@ -26101,16 +26106,16 @@
         <v>2598</v>
       </c>
       <c r="C676" s="7" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="D676" s="7" t="s">
         <v>1960</v>
       </c>
       <c r="E676" s="7" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="F676" s="7" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="G676" s="7" t="s">
         <v>1961</v>
@@ -26127,7 +26132,7 @@
         <v>2598</v>
       </c>
       <c r="C677" s="7" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="D677" s="7" t="s">
         <v>2028</v>
@@ -26136,10 +26141,10 @@
         <v>2129</v>
       </c>
       <c r="F677" s="7" t="s">
+        <v>2759</v>
+      </c>
+      <c r="G677" s="7" t="s">
         <v>2760</v>
-      </c>
-      <c r="G677" s="7" t="s">
-        <v>2761</v>
       </c>
       <c r="H677" s="8" t="s">
         <v>21</v>
@@ -26153,19 +26158,19 @@
         <v>2598</v>
       </c>
       <c r="C678" s="7" t="s">
+        <v>2761</v>
+      </c>
+      <c r="D678" s="7" t="s">
         <v>2762</v>
       </c>
-      <c r="D678" s="7" t="s">
+      <c r="E678" s="7" t="s">
         <v>2763</v>
       </c>
-      <c r="E678" s="7" t="s">
+      <c r="F678" s="7" t="s">
         <v>2764</v>
       </c>
-      <c r="F678" s="7" t="s">
+      <c r="G678" s="7" t="s">
         <v>2765</v>
-      </c>
-      <c r="G678" s="7" t="s">
-        <v>2766</v>
       </c>
       <c r="H678" s="8" t="s">
         <v>38</v>
